--- a/主要指数介绍-发布日期超过10年的(2016年1月1日之前的).xlsx
+++ b/主要指数介绍-发布日期超过10年的(2016年1月1日之前的).xlsx
@@ -1586,16 +1586,16 @@
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.141592920354" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.36283185840708" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.53097345132743" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="14.212389380531" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7256637168142" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="14" width="8.53097345132743" style="2" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="7.53097345132743" style="2" hidden="1" customWidth="1"/>
-    <col min="16" max="19" width="8.53097345132743" style="1" hidden="1" customWidth="1"/>
-    <col min="20" max="22" width="10.5929203539823" style="1" hidden="1" customWidth="1"/>
-    <col min="23" max="26" width="8.53097345132743" style="1" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="9.56637168141593" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.36283185840708" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.53097345132743" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.212389380531" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.7256637168142" style="2" customWidth="1"/>
+    <col min="6" max="14" width="8.53097345132743" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.53097345132743" style="2" customWidth="1"/>
+    <col min="16" max="19" width="8.53097345132743" style="1" customWidth="1"/>
+    <col min="20" max="22" width="10.5929203539823" style="1" customWidth="1"/>
+    <col min="23" max="26" width="8.53097345132743" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9.56637168141593" style="1" customWidth="1"/>
     <col min="28" max="28" width="22.2035398230088" style="1" customWidth="1"/>
     <col min="29" max="29" width="9.56637168141593" style="1" customWidth="1"/>
     <col min="30" max="30" width="28.6725663716814" style="3" customWidth="1"/>
